--- a/dev/StructureDefinition-bc-organization-affiliation.xlsx
+++ b/dev/StructureDefinition-bc-organization-affiliation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-23T20:38:35+00:00</t>
+    <t>2026-01-23T00:06:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2080,7 +2080,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>140</v>
       </c>
@@ -2188,7 +2188,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>145</v>
       </c>
@@ -2406,7 +2406,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>155</v>
       </c>
@@ -2514,7 +2514,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>162</v>
       </c>
@@ -2626,7 +2626,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>171</v>
       </c>
@@ -2736,7 +2736,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>180</v>
       </c>
@@ -2844,7 +2844,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
         <v>187</v>
       </c>
@@ -3060,7 +3060,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>196</v>
       </c>
@@ -3276,7 +3276,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
         <v>211</v>
       </c>
@@ -3710,12 +3710,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AL24">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
